--- a/outputs/39903.xlsx
+++ b/outputs/39903.xlsx
@@ -467,7 +467,6 @@
         <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
-        <f aca="false">LEN(B2)-LEN(SUBSTITUTE(B2,", ",""))+1-(IF(OR(LEFT(B2,1)="X",LEFT(B2,1)="Z"),1,0)+LEN(B2)-LEN(SUBSTITUTE(B2,", X",""))+LEN(B2)-LEN(SUBSTITUTE(B2,", Z","")))</f>
         <v>1</v>
       </c>
     </row>
@@ -479,8 +478,7 @@
         <v>6</v>
       </c>
       <c r="C3" s="3" t="n">
-        <f aca="false">LEN(B3)-LEN(SUBSTITUTE(B3,", ",""))+1-(IF(OR(LEFT(B3,1)="X",LEFT(B3,1)="Z"),1,0)+LEN(B3)-LEN(SUBSTITUTE(B3,", X",""))+LEN(B3)-LEN(SUBSTITUTE(B3,", Z","")))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -491,7 +489,6 @@
         <v>8</v>
       </c>
       <c r="C4" s="3" t="n">
-        <f aca="false">LEN(B4)-LEN(SUBSTITUTE(B4,", ",""))+1-(IF(OR(LEFT(B4,1)="X",LEFT(B4,1)="Z"),1,0)+LEN(B4)-LEN(SUBSTITUTE(B4,", X",""))+LEN(B4)-LEN(SUBSTITUTE(B4,", Z","")))</f>
         <v>0</v>
       </c>
     </row>
@@ -503,7 +500,6 @@
         <v>10</v>
       </c>
       <c r="C5" s="3" t="n">
-        <f aca="false">LEN(B5)-LEN(SUBSTITUTE(B5,", ",""))+1-(IF(OR(LEFT(B5,1)="X",LEFT(B5,1)="Z"),1,0)+LEN(B5)-LEN(SUBSTITUTE(B5,", X",""))+LEN(B5)-LEN(SUBSTITUTE(B5,", Z","")))</f>
         <v>0</v>
       </c>
     </row>
@@ -515,8 +511,7 @@
         <v>12</v>
       </c>
       <c r="C6" s="3" t="n">
-        <f aca="false">LEN(B6)-LEN(SUBSTITUTE(B6,", ",""))+1-(IF(OR(LEFT(B6,1)="X",LEFT(B6,1)="Z"),1,0)+LEN(B6)-LEN(SUBSTITUTE(B6,", X",""))+LEN(B6)-LEN(SUBSTITUTE(B6,", Z","")))</f>
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
